--- a/5G ANTS Daily Update 08 Dec 2025.xlsx
+++ b/5G ANTS Daily Update 08 Dec 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ODS7493\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F0803AF-FF1E-4FBC-8685-81148E9FD1E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8183C9AF-03B2-46F0-BD6E-26EE5E437A86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{933DD8AB-2916-4153-814A-44F164BA69EB}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7145" uniqueCount="3293">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7327" uniqueCount="3357">
   <si>
     <t>Circle</t>
   </si>
@@ -14199,6 +14199,296 @@
 4. For sites with NOKIA OEM, validate using Drive Idle, and for other OEMs, validate using Static Idle. In both Drive and Static Idle, the UE should latch from NR to LTE and from LTE to NR. In LTE, the UE should latch on the band that corresponds to the configured anchor layer.
 5. Kindly verify that the UE in connected mode is switching from the preferred anchor layer to NR as expected.
 6. While performing the YouTube test for both sectors, please ensure that the video is playing successfully in the script before saving the log file.</t>
+  </si>
+  <si>
+    <t>MPST7532_STA_P40</t>
+  </si>
+  <si>
+    <t>13-Jan-2026 11:19 PM</t>
+  </si>
+  <si>
+    <t>MNTY06_SA_TSR_P40</t>
+  </si>
+  <si>
+    <t>13-Jan-2026 9:00 PM</t>
+  </si>
+  <si>
+    <t>1. sector id (s)
+2. PCI
+3. % samples better than -105 dBm
+4. Serving SSB beam steering
+5. SCG addition after VoLTE call released
+6. With 5G SIM (Idle)
+7. With 5G SIM (Connected)
+8. With 5G SIM during VoLTE call
+9. Median PDCP DL​ Throughput
+10. Median PDCP UL Throughput
+11. Median PUSCH UL​ Throughput
+12. SgNB Addition time (ms)
+13. UE Steering (Idle) : Non anchor/anchor to preferred anchor
+14. DL Split bearer
+15. UL Split bearer &amp; leg switching
+16. MCG,SCG bearer switching</t>
+  </si>
+  <si>
+    <t>1. 
+2. Static All
+3. Mobility DL
+4. Mobility DL
+5. Static VoLTE MO
+6. Drive DL
+7. Drive DL
+8. Drive DL
+9. Mobility DL
+10. Mobility UL
+11. Mobility UL
+12. Static ATDT
+13. Static Idle
+14. Mobility DL
+15. Mobility UL
+16. Mobility DL</t>
+  </si>
+  <si>
+    <t>1. 
+2. The PCI uploaded in the site database is not aligned with the actual on-site servings. Kindly verify the configured PCI and update the database accordingly to avoid inconsistency in reporting.
+3. This issue may occur due to no drive coverage in the failed sector or the failed sector PCI not serving in the current drive. Kindly perform additional drive tests and ensure full DTR coverage.
+4. Kindly add drive coverage in the failed sector and verify that the Beam Index servings are meeting the acceptance criteria.
+5. VoLTE Long Call MO – The SCG count after VoLTE call release should be equal to or greater than the total number of calls in the logfile. The KPI has failed because the SCG count is lower than the number of calls. Kindly exclude the existing logfile. While creating a new logfile, ensure the same site is serving in 4G and keep test files downloading in the background during static tests to support SCG addition.
+6. This issue may occur due to no drive coverage in the failed sector or the failed sector PCI not serving in the current drive. Kindly perform additional drive tests and ensure full DTR coverage.
+7. This issue may occur due to no drive coverage in the failed sector or the failed sector PCI not serving in the current drive. Kindly perform additional drive tests and ensure full DTR coverage.
+8. This issue may occur due to no drive coverage in the failed sector or the failed sector PCI not serving in the current drive. Kindly perform additional drive tests and ensure full DTR coverage.
+9. The Median PDCP DL Throughput is reported as 0. Kindly add or exclude a logfile in the DL drive so the median value can update. It is recommended to add a new logfile and collect maximum throughput samples in a good coverage area.
+10. The Median PDCP UL Throughput is reported as 0. Kindly add or exclude a logfile in the DL drive so the median value can update. It is recommended to add a new logfile and collect maximum throughput samples in a good coverage area.
+11. The Median PUSCH UL Throughput is reported as 0. Kindly add or exclude a logfile in the DL drive so the median value can update. It is recommended to add a new logfile and collect maximum throughput samples in a good coverage area.
+12. Exclue ATDT Logfile and Create New Sgnb Addition Time Is Very High. It Should Be &lt;150 Ms. To Achieve This, Perform Static Test In Main Lobe And Keep Test Files Downloading In Background. Also, Ensure 4G Serving Cell Belongs To The Same Site. Exclude The Existing Logfile First
+13. For sites with NOKIA OEM, validate using Drive Idle, and for other OEMs, validate using Static Idle. In both Drive and Static Idle, the UE should latch from NR to LTE and from LTE to NR. In LTE, the UE should latch on the band that corresponds to the configured anchor layer.
+14. This issue may occur due to no drive coverage in the failed sector or the failed sector PCI not serving in the current drive. Kindly perform additional drive tests and ensure full DTR coverage.
+15. This issue may occur due to no drive coverage in the failed sector or the failed sector PCI not serving in the current drive. Kindly perform additional drive tests and ensure full DTR coverage.
+16. This issue may occur due to no drive coverage in the failed sector or the failed sector PCI not serving in the current drive. Kindly perform additional drive tests and ensure full DTR coverage.</t>
+  </si>
+  <si>
+    <t>13-Jan-2026 7:31 PM</t>
+  </si>
+  <si>
+    <t>SMBL63_MOR_P41</t>
+  </si>
+  <si>
+    <t>13-Jan-2026 6:38 PM</t>
+  </si>
+  <si>
+    <t>1. MO Call (pass/fail)
+2. MT Call (pass/fail)
+3. CSFB Call (pass/fail)
+4. QCI Verification
+5. Video Streaming</t>
+  </si>
+  <si>
+    <t>1. Static VoLTE MO
+2. Static VoLTE MT
+3. Static CSFB MO
+4. Static All
+5. Static Yotube Streaming</t>
+  </si>
+  <si>
+    <t>1. VoLTE Long Call MO – As per Bharti acceptance criteria, a minimum of 3 successful call setups are required without any blocked call. Kindly perform at least 3 successful MO calls.
+2. VoLTE Long Call MT – As per Bharti acceptance criteria, a minimum of 3 successful call setups are required without any blocked call. Kindly perform at least 3 successful MT calls.
+3. CSFB MO – As per Bharti acceptance criteria, a minimum of 3 successful call setups are required without any blocked call. Kindly perform at least 3 successful MO  calls.
+4. If the DT tool is TEMS, verify the QCI combined value in the DL drive. If the DT tool is AZQ, verify it in Static All. The QCI combined value must meet the acceptance criteria.
+5. While performing the YouTube test for both sectors, please ensure that the video is playing successfully in the script before saving the log file.</t>
+  </si>
+  <si>
+    <t>MYLA23_CHN_P41</t>
+  </si>
+  <si>
+    <t>13-Jan-2026 6:34 PM</t>
+  </si>
+  <si>
+    <t>KO0898_KOL_P40</t>
+  </si>
+  <si>
+    <t>AGA193_AGR_P40</t>
+  </si>
+  <si>
+    <t>13-Jan-2026 6:54 PM</t>
+  </si>
+  <si>
+    <t>1. VoLTE Long Call MO – The SCG count after VoLTE call release should be equal to or greater than the total number of calls in the logfile. The KPI has failed because the SCG count is lower than the number of calls. Kindly exclude the existing logfile. While creating a new logfile, ensure the same site is serving in 4G and keep test files downloading in the background during static tests to support SCG addition.
+2. Peak PUSCH UL throughput is not meeting the acceptance criteria, and if the value is 0, it indicates that it was not recorded in the logfile. Kindly exclude the logfile and create a new one, and verify the maximum value of PUSCH Throughput in the NR tab.
+3. Please update the AZQ app to version v3.2.822.apk specifically for the YouTube test.Kindly note that all other tests must continue to be performed using version v3.2.237.While performing the YouTube test, please ensure that the video is successfully playing in the script before saving the log file</t>
+  </si>
+  <si>
+    <t>PLYUR4_KRU_P40</t>
+  </si>
+  <si>
+    <t>13-Jan-2026 6:25 PM</t>
+  </si>
+  <si>
+    <t>KMGLM8_KRG_P40</t>
+  </si>
+  <si>
+    <t>13-Jan-2026 6:22 PM</t>
+  </si>
+  <si>
+    <t>13-Jan-2026 1:24 PM</t>
+  </si>
+  <si>
+    <t>1. VoLTE Long Call MO – The SCG count after VoLTE call release should be equal to or greater than the total number of calls in the logfile. The KPI has failed because the SCG count is lower than the number of calls. Kindly exclude the existing logfile. While creating a new logfile, ensure the same site is serving in 4G and keep test files downloading in the background during static tests to support SCG addition.
+2. Peak PUSCH UL throughput is not meeting the acceptance criteria, and if the value is 0, it indicates that it was not recorded in the logfile. Kindly exclude the logfile and create a new one, and verify the maximum value of PUSCH Throughput in the NR tab.</t>
+  </si>
+  <si>
+    <t>JISBH-02_PAT_P41</t>
+  </si>
+  <si>
+    <t>12-Jan-2026 9:10 PM</t>
+  </si>
+  <si>
+    <t>AZKO10_TSR_P40</t>
+  </si>
+  <si>
+    <t>12-Jan-2026 8:40 PM</t>
+  </si>
+  <si>
+    <t>1. SCG addition after VoLTE call released
+2. Downlink Peak MCS - 5G
+3. Peak Rank - 5G
+4. SgNB Addition time (ms)
+5. UE Steering (Idle) : Non anchor/anchor to preferred anchor</t>
+  </si>
+  <si>
+    <t>1. Static VoLTE MO
+2. Static DL
+3. Static DL
+4. Static ATDT
+5. Static Idle</t>
+  </si>
+  <si>
+    <t>1. VoLTE Long Call MO – The SCG count after VoLTE call release should be equal to or greater than the total number of calls in the logfile. The KPI has failed because the SCG count is lower than the number of calls. Kindly exclude the existing logfile. While creating a new logfile, ensure the same site is serving in 4G and keep test files downloading in the background during static tests to support SCG addition.
+2. Peak MCS is not meeting the acceptance criteria. Kindly redo the test and verify that the value meets the required threshold. To achieve the desired MCS, perform the test in the main lobe of the cell within a good coverage area.
+3. Peak Rank is not meeting the acceptance criteria. Kindly redo the test and verify that the value meets the required threshold. To achieve the desired MCS, perform the test in the main lobe of the cell within a good coverage area.
+4. Exclue ATDT Logfile and Create New Sgnb Addition Time Is Very High. It Should Be &lt;150 Ms. To Achieve This, Perform Static Test In Main Lobe And Keep Test Files Downloading In Background. Also, Ensure 4G Serving Cell Belongs To The Same Site. Exclude The Existing Logfile First
+5. For sites with NOKIA OEM, validate using Drive Idle, and for other OEMs, validate using Static Idle. In both Drive and Static Idle, the UE should latch from NR to LTE and from LTE to NR. In LTE, the UE should latch on the band that corresponds to the configured anchor layer.</t>
+  </si>
+  <si>
+    <t>LKTH676_AMS_P40</t>
+  </si>
+  <si>
+    <t>12-Jan-2026 7:40 PM</t>
+  </si>
+  <si>
+    <t>1. Serving SSB beam steering
+2. Peak Rank - 5G</t>
+  </si>
+  <si>
+    <t>1. Mobility DL
+2. Static DL</t>
+  </si>
+  <si>
+    <t>1. Kindly add drive coverage in the failed sector and verify that the Beam Index servings are meeting the acceptance criteria.
+2. Peak Rank is not meeting the acceptance criteria. Kindly redo the test and verify that the value meets the required threshold. To achieve the desired MCS, perform the test in the main lobe of the cell within a good coverage area.</t>
+  </si>
+  <si>
+    <t>12-Jan-2026 6:37 PM</t>
+  </si>
+  <si>
+    <t>12-Jan-2026 4:04 PM</t>
+  </si>
+  <si>
+    <t>14-Jan-2026 10:10 PM</t>
+  </si>
+  <si>
+    <t>1. MT Call (pass/fail)</t>
+  </si>
+  <si>
+    <t>1. Static VoLTE MT</t>
+  </si>
+  <si>
+    <t>1. VoLTE Long Call MT – As per Bharti acceptance criteria, a minimum of 3 successful call setups are required without any blocked call. Kindly perform at least 3 successful MT calls.</t>
+  </si>
+  <si>
+    <t>KO0143_KOL_P40</t>
+  </si>
+  <si>
+    <t>14-Jan-2026 9:48 PM</t>
+  </si>
+  <si>
+    <t>PUN3830_PNE_P40</t>
+  </si>
+  <si>
+    <t>14-Jan-2026 8:24 PM</t>
+  </si>
+  <si>
+    <t>1. eRAB setup success</t>
+  </si>
+  <si>
+    <t>1. Static ATDT – This is a 4G KPI. In ANTS, select the 4G filter and verify that the LTE Default EPS Bearer Request count matches the LTE Default EPS Bearer Activated count. If there is any mismatch, kindly exclude the logfile and create a new one.</t>
+  </si>
+  <si>
+    <t>14-Jan-2026 6:08 PM</t>
+  </si>
+  <si>
+    <t>14-Jan-2026 5:28 PM</t>
+  </si>
+  <si>
+    <t>BHDHA-127_PAT_P40</t>
+  </si>
+  <si>
+    <t>14-Jan-2026 5:26 PM</t>
+  </si>
+  <si>
+    <t>1. eRAB setup success
+2. SgNB addition Success (ENDC Setup)
+3. Peak PUSCH UL Throughput
+4. SgNB Addition time (ms)
+5. UE Steering (Idle) : Non anchor/anchor to preferred anchor
+6. Video Streaming  (ms)</t>
+  </si>
+  <si>
+    <t>1. Static ATDT
+2. Static ATDT
+3. Static UL
+4. Static ATDT
+5. Static Idle
+6. Static Yotube Streaming</t>
+  </si>
+  <si>
+    <t>1. Static ATDT – This is a 4G KPI. In ANTS, select the 4G filter and verify that the LTE Default EPS Bearer Request count matches the LTE Default EPS Bearer Activated count. If there is any mismatch, kindly exclude the logfile and create a new one.
+2. Static ATDT –  Verify that the NR ENDC RRC Reconfiguration count matches the NR ENDC RRC Reconfiguration Complete count. If there is any mismatch, kindly exclude the logfile and create a new one.
+3. Peak PUSCH UL throughput is not meeting the acceptance criteria, and if the value is 0, it indicates that it was not recorded in the logfile. Kindly exclude the logfile and create a new one, and verify the maximum value of PUSCH Throughput in the NR tab.
+4. Exclue ATDT Logfile and Create New Sgnb Addition Time Is Very High. It Should Be &lt;150 Ms. To Achieve This, Perform Static Test In Main Lobe And Keep Test Files Downloading In Background. Also, Ensure 4G Serving Cell Belongs To The Same Site. Exclude The Existing Logfile First
+5. For sites with NOKIA OEM, validate using Drive Idle, and for other OEMs, validate using Static Idle. In both Drive and Static Idle, the UE should latch from NR to LTE and from LTE to NR. In LTE, the UE should latch on the band that corresponds to the configured anchor layer.
+6. Please update the AZQ app to version v3.2.822.apk specifically for the YouTube test.Kindly note that all other tests must continue to be performed using version v3.2.237.While performing the YouTube test, please ensure that the video is successfully playing in the script before saving the log file</t>
+  </si>
+  <si>
+    <t>14-Jan-2026 5:20 PM</t>
+  </si>
+  <si>
+    <t>14-Jan-2026 4:41 PM</t>
+  </si>
+  <si>
+    <t>14-Jan-2026 4:26 PM</t>
+  </si>
+  <si>
+    <t>14-Jan-2026 4:43 PM</t>
+  </si>
+  <si>
+    <t>PUN3120_PNE_P40</t>
+  </si>
+  <si>
+    <t>14-Jan-2026 3:18 PM</t>
+  </si>
+  <si>
+    <t>1. Peak PDSCH DL Throughput
+2. Peak PUSCH UL Throughput
+3. Ping/Round trip time(ms)
+4. SgNB Addition time (ms)
+5. Video Streaming  (ms)</t>
+  </si>
+  <si>
+    <t>1. Peak PDSCH DL Throughput is not meeting the acceptance criteria, and if the value is 0, it indicates that it was not recorded in the logfile. Kindly exclude the logfile and create a new one, and verify the maximum value of PDSCH Throughput in the NR tab.
+2. Peak PUSCH UL throughput is not meeting the acceptance criteria, and if the value is 0, it indicates that it was not recorded in the logfile. Kindly exclude the logfile and create a new one, and verify the maximum value of PUSCH Throughput in the NR tab.
+3. Ping is not meeting the acceptance criteria. The average ping value across all logfiles should be less than 50 ms. Kindly exclude the logfile where the average value exceeds 50 ms and redo the test.”
+4. Exclue ATDT Logfile and Create New Sgnb Addition Time Is Very High. It Should Be &lt;150 Ms. To Achieve This, Perform Static Test In Main Lobe And Keep Test Files Downloading In Background. Also, Ensure 4G Serving Cell Belongs To The Same Site. Exclude The Existing Logfile First
+5. Please update the AZQ app to version v3.2.822.apk specifically for the YouTube test.Kindly note that all other tests must continue to be performed using version v3.2.237.While performing the YouTube test, please ensure that the video is successfully playing in the script before saving the log file</t>
   </si>
 </sst>
 </file>
@@ -14683,7 +14973,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{450A2877-A455-427A-9170-EAD9C8461604}">
-  <dimension ref="A1:G1126"/>
+  <dimension ref="A1:G1152"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.6328125" bestFit="1" customWidth="1"/>
@@ -39121,6 +39411,604 @@
         <v>3292</v>
       </c>
     </row>
+    <row r="1127" spans="1:7" ht="28.5" x14ac:dyDescent="0.35">
+      <c r="A1127" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1127" s="8" t="s">
+        <v>3293</v>
+      </c>
+      <c r="C1127" s="7" t="s">
+        <v>3294</v>
+      </c>
+      <c r="D1127" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1127" s="10" t="s">
+        <v>2356</v>
+      </c>
+      <c r="F1127" s="11" t="s">
+        <v>2357</v>
+      </c>
+      <c r="G1127" s="12" t="s">
+        <v>2358</v>
+      </c>
+    </row>
+    <row r="1128" spans="1:7" ht="361" x14ac:dyDescent="0.35">
+      <c r="A1128" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1128" s="8" t="s">
+        <v>3295</v>
+      </c>
+      <c r="C1128" s="7" t="s">
+        <v>3296</v>
+      </c>
+      <c r="D1128" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1128" s="10" t="s">
+        <v>3297</v>
+      </c>
+      <c r="F1128" s="11" t="s">
+        <v>3298</v>
+      </c>
+      <c r="G1128" s="12" t="s">
+        <v>3299</v>
+      </c>
+    </row>
+    <row r="1129" spans="1:7" ht="66.5" x14ac:dyDescent="0.35">
+      <c r="A1129" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1129" s="8" t="s">
+        <v>3271</v>
+      </c>
+      <c r="C1129" s="7" t="s">
+        <v>3300</v>
+      </c>
+      <c r="D1129" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1129" s="10" t="s">
+        <v>2609</v>
+      </c>
+      <c r="F1129" s="11" t="s">
+        <v>2610</v>
+      </c>
+      <c r="G1129" s="12" t="s">
+        <v>2611</v>
+      </c>
+    </row>
+    <row r="1130" spans="1:7" ht="95" x14ac:dyDescent="0.35">
+      <c r="A1130" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1130" s="8" t="s">
+        <v>3301</v>
+      </c>
+      <c r="C1130" s="7" t="s">
+        <v>3302</v>
+      </c>
+      <c r="D1130" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1130" s="10" t="s">
+        <v>3303</v>
+      </c>
+      <c r="F1130" s="11" t="s">
+        <v>3304</v>
+      </c>
+      <c r="G1130" s="12" t="s">
+        <v>3305</v>
+      </c>
+    </row>
+    <row r="1131" spans="1:7" ht="38" x14ac:dyDescent="0.35">
+      <c r="A1131" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="B1131" s="8" t="s">
+        <v>3306</v>
+      </c>
+      <c r="C1131" s="7" t="s">
+        <v>3307</v>
+      </c>
+      <c r="D1131" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1131" s="10" t="s">
+        <v>2757</v>
+      </c>
+      <c r="F1131" s="11" t="s">
+        <v>2758</v>
+      </c>
+      <c r="G1131" s="12" t="s">
+        <v>2759</v>
+      </c>
+    </row>
+    <row r="1132" spans="1:7" ht="294.5" x14ac:dyDescent="0.35">
+      <c r="A1132" s="7" t="s">
+        <v>2201</v>
+      </c>
+      <c r="B1132" s="8" t="s">
+        <v>3308</v>
+      </c>
+      <c r="C1132" s="7" t="s">
+        <v>3302</v>
+      </c>
+      <c r="D1132" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1132" s="10" t="s">
+        <v>2953</v>
+      </c>
+      <c r="F1132" s="11" t="s">
+        <v>2954</v>
+      </c>
+      <c r="G1132" s="12" t="s">
+        <v>2955</v>
+      </c>
+    </row>
+    <row r="1133" spans="1:7" ht="95" x14ac:dyDescent="0.35">
+      <c r="A1133" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1133" s="8" t="s">
+        <v>3309</v>
+      </c>
+      <c r="C1133" s="7" t="s">
+        <v>3310</v>
+      </c>
+      <c r="D1133" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1133" s="10" t="s">
+        <v>2709</v>
+      </c>
+      <c r="F1133" s="11" t="s">
+        <v>2710</v>
+      </c>
+      <c r="G1133" s="12" t="s">
+        <v>3311</v>
+      </c>
+    </row>
+    <row r="1134" spans="1:7" ht="28.5" x14ac:dyDescent="0.35">
+      <c r="A1134" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1134" s="8" t="s">
+        <v>3312</v>
+      </c>
+      <c r="C1134" s="7" t="s">
+        <v>3313</v>
+      </c>
+      <c r="D1134" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1134" s="10" t="s">
+        <v>2356</v>
+      </c>
+      <c r="F1134" s="11" t="s">
+        <v>2357</v>
+      </c>
+      <c r="G1134" s="12" t="s">
+        <v>2358</v>
+      </c>
+    </row>
+    <row r="1135" spans="1:7" ht="28.5" x14ac:dyDescent="0.35">
+      <c r="A1135" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1135" s="8" t="s">
+        <v>3314</v>
+      </c>
+      <c r="C1135" s="7" t="s">
+        <v>3315</v>
+      </c>
+      <c r="D1135" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1135" s="10" t="s">
+        <v>2356</v>
+      </c>
+      <c r="F1135" s="11" t="s">
+        <v>2357</v>
+      </c>
+      <c r="G1135" s="12" t="s">
+        <v>2358</v>
+      </c>
+    </row>
+    <row r="1136" spans="1:7" ht="66.5" x14ac:dyDescent="0.35">
+      <c r="A1136" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1136" s="8" t="s">
+        <v>3027</v>
+      </c>
+      <c r="C1136" s="7" t="s">
+        <v>3316</v>
+      </c>
+      <c r="D1136" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1136" s="10" t="s">
+        <v>2667</v>
+      </c>
+      <c r="F1136" s="11" t="s">
+        <v>2668</v>
+      </c>
+      <c r="G1136" s="12" t="s">
+        <v>3317</v>
+      </c>
+    </row>
+    <row r="1137" spans="1:7" ht="38" x14ac:dyDescent="0.35">
+      <c r="A1137" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1137" s="8" t="s">
+        <v>3318</v>
+      </c>
+      <c r="C1137" s="7" t="s">
+        <v>3319</v>
+      </c>
+      <c r="D1137" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1137" s="10" t="s">
+        <v>2389</v>
+      </c>
+      <c r="F1137" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="G1137" s="12" t="s">
+        <v>3254</v>
+      </c>
+    </row>
+    <row r="1138" spans="1:7" ht="133" x14ac:dyDescent="0.35">
+      <c r="A1138" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1138" s="8" t="s">
+        <v>3320</v>
+      </c>
+      <c r="C1138" s="7" t="s">
+        <v>3321</v>
+      </c>
+      <c r="D1138" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1138" s="10" t="s">
+        <v>3322</v>
+      </c>
+      <c r="F1138" s="11" t="s">
+        <v>3323</v>
+      </c>
+      <c r="G1138" s="12" t="s">
+        <v>3324</v>
+      </c>
+    </row>
+    <row r="1139" spans="1:7" ht="38" x14ac:dyDescent="0.35">
+      <c r="A1139" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1139" s="8" t="s">
+        <v>3325</v>
+      </c>
+      <c r="C1139" s="7" t="s">
+        <v>3326</v>
+      </c>
+      <c r="D1139" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1139" s="10" t="s">
+        <v>3327</v>
+      </c>
+      <c r="F1139" s="11" t="s">
+        <v>3328</v>
+      </c>
+      <c r="G1139" s="12" t="s">
+        <v>3329</v>
+      </c>
+    </row>
+    <row r="1140" spans="1:7" ht="66.5" x14ac:dyDescent="0.35">
+      <c r="A1140" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1140" s="8" t="s">
+        <v>3206</v>
+      </c>
+      <c r="C1140" s="7" t="s">
+        <v>3330</v>
+      </c>
+      <c r="D1140" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1140" s="10" t="s">
+        <v>2609</v>
+      </c>
+      <c r="F1140" s="11" t="s">
+        <v>2610</v>
+      </c>
+      <c r="G1140" s="12" t="s">
+        <v>2611</v>
+      </c>
+    </row>
+    <row r="1141" spans="1:7" ht="76" x14ac:dyDescent="0.35">
+      <c r="A1141" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1141" s="8" t="s">
+        <v>3279</v>
+      </c>
+      <c r="C1141" s="7" t="s">
+        <v>3331</v>
+      </c>
+      <c r="D1141" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1141" s="10" t="s">
+        <v>2863</v>
+      </c>
+      <c r="F1141" s="11" t="s">
+        <v>2864</v>
+      </c>
+      <c r="G1141" s="12" t="s">
+        <v>3281</v>
+      </c>
+    </row>
+    <row r="1142" spans="1:7" ht="19" x14ac:dyDescent="0.35">
+      <c r="A1142" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="B1142" s="8" t="s">
+        <v>3306</v>
+      </c>
+      <c r="C1142" s="7" t="s">
+        <v>3332</v>
+      </c>
+      <c r="D1142" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1142" s="10" t="s">
+        <v>3333</v>
+      </c>
+      <c r="F1142" s="11" t="s">
+        <v>3334</v>
+      </c>
+      <c r="G1142" s="12" t="s">
+        <v>3335</v>
+      </c>
+    </row>
+    <row r="1143" spans="1:7" ht="38" x14ac:dyDescent="0.35">
+      <c r="A1143" s="7" t="s">
+        <v>2201</v>
+      </c>
+      <c r="B1143" s="8" t="s">
+        <v>3336</v>
+      </c>
+      <c r="C1143" s="7" t="s">
+        <v>3337</v>
+      </c>
+      <c r="D1143" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1143" s="10" t="s">
+        <v>2524</v>
+      </c>
+      <c r="F1143" s="11" t="s">
+        <v>2525</v>
+      </c>
+      <c r="G1143" s="12" t="s">
+        <v>2526</v>
+      </c>
+    </row>
+    <row r="1144" spans="1:7" ht="28.5" x14ac:dyDescent="0.35">
+      <c r="A1144" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1144" s="8" t="s">
+        <v>3338</v>
+      </c>
+      <c r="C1144" s="7" t="s">
+        <v>3339</v>
+      </c>
+      <c r="D1144" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1144" s="10" t="s">
+        <v>3340</v>
+      </c>
+      <c r="F1144" s="11" t="s">
+        <v>2361</v>
+      </c>
+      <c r="G1144" s="12" t="s">
+        <v>3341</v>
+      </c>
+    </row>
+    <row r="1145" spans="1:7" ht="38" x14ac:dyDescent="0.35">
+      <c r="A1145" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1145" s="8" t="s">
+        <v>3271</v>
+      </c>
+      <c r="C1145" s="7" t="s">
+        <v>3342</v>
+      </c>
+      <c r="D1145" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1145" s="10" t="s">
+        <v>2524</v>
+      </c>
+      <c r="F1145" s="11" t="s">
+        <v>2525</v>
+      </c>
+      <c r="G1145" s="12" t="s">
+        <v>2526</v>
+      </c>
+    </row>
+    <row r="1146" spans="1:7" ht="47.5" x14ac:dyDescent="0.35">
+      <c r="A1146" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1146" s="8" t="s">
+        <v>2542</v>
+      </c>
+      <c r="C1146" s="7" t="s">
+        <v>3343</v>
+      </c>
+      <c r="D1146" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1146" s="10" t="s">
+        <v>2544</v>
+      </c>
+      <c r="F1146" s="11" t="s">
+        <v>2545</v>
+      </c>
+      <c r="G1146" s="12" t="s">
+        <v>2546</v>
+      </c>
+    </row>
+    <row r="1147" spans="1:7" ht="161.5" x14ac:dyDescent="0.35">
+      <c r="A1147" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1147" s="8" t="s">
+        <v>3344</v>
+      </c>
+      <c r="C1147" s="7" t="s">
+        <v>3345</v>
+      </c>
+      <c r="D1147" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1147" s="10" t="s">
+        <v>3346</v>
+      </c>
+      <c r="F1147" s="11" t="s">
+        <v>3347</v>
+      </c>
+      <c r="G1147" s="12" t="s">
+        <v>3348</v>
+      </c>
+    </row>
+    <row r="1148" spans="1:7" ht="76" x14ac:dyDescent="0.35">
+      <c r="A1148" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1148" s="8" t="s">
+        <v>3279</v>
+      </c>
+      <c r="C1148" s="7" t="s">
+        <v>3349</v>
+      </c>
+      <c r="D1148" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1148" s="10" t="s">
+        <v>2863</v>
+      </c>
+      <c r="F1148" s="11" t="s">
+        <v>2864</v>
+      </c>
+      <c r="G1148" s="12" t="s">
+        <v>3281</v>
+      </c>
+    </row>
+    <row r="1149" spans="1:7" ht="19" x14ac:dyDescent="0.35">
+      <c r="A1149" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="B1149" s="8" t="s">
+        <v>2909</v>
+      </c>
+      <c r="C1149" s="7" t="s">
+        <v>3350</v>
+      </c>
+      <c r="D1149" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1149" s="10" t="s">
+        <v>2705</v>
+      </c>
+      <c r="F1149" s="11" t="s">
+        <v>2706</v>
+      </c>
+      <c r="G1149" s="12" t="s">
+        <v>2707</v>
+      </c>
+    </row>
+    <row r="1150" spans="1:7" ht="142.5" x14ac:dyDescent="0.35">
+      <c r="A1150" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1150" s="8" t="s">
+        <v>1573</v>
+      </c>
+      <c r="C1150" s="7" t="s">
+        <v>3351</v>
+      </c>
+      <c r="D1150" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1150" s="10" t="s">
+        <v>2689</v>
+      </c>
+      <c r="F1150" s="11" t="s">
+        <v>2690</v>
+      </c>
+      <c r="G1150" s="12" t="s">
+        <v>2691</v>
+      </c>
+    </row>
+    <row r="1151" spans="1:7" ht="66.5" x14ac:dyDescent="0.35">
+      <c r="A1151" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1151" s="8" t="s">
+        <v>2716</v>
+      </c>
+      <c r="C1151" s="7" t="s">
+        <v>3352</v>
+      </c>
+      <c r="D1151" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1151" s="10" t="s">
+        <v>2425</v>
+      </c>
+      <c r="F1151" s="11" t="s">
+        <v>2426</v>
+      </c>
+      <c r="G1151" s="12" t="s">
+        <v>2427</v>
+      </c>
+    </row>
+    <row r="1152" spans="1:7" ht="133" x14ac:dyDescent="0.35">
+      <c r="A1152" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1152" s="8" t="s">
+        <v>3353</v>
+      </c>
+      <c r="C1152" s="7" t="s">
+        <v>3354</v>
+      </c>
+      <c r="D1152" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1152" s="10" t="s">
+        <v>3355</v>
+      </c>
+      <c r="F1152" s="11" t="s">
+        <v>3068</v>
+      </c>
+      <c r="G1152" s="12" t="s">
+        <v>3356</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/5G ANTS Daily Update 08 Dec 2025.xlsx
+++ b/5G ANTS Daily Update 08 Dec 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ODS7493\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8183C9AF-03B2-46F0-BD6E-26EE5E437A86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D99A95A0-BA5A-45BA-9063-464DC2C518F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{933DD8AB-2916-4153-814A-44F164BA69EB}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7327" uniqueCount="3357">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7509" uniqueCount="3432">
   <si>
     <t>Circle</t>
   </si>
@@ -14489,6 +14489,320 @@
 3. Ping is not meeting the acceptance criteria. The average ping value across all logfiles should be less than 50 ms. Kindly exclude the logfile where the average value exceeds 50 ms and redo the test.”
 4. Exclue ATDT Logfile and Create New Sgnb Addition Time Is Very High. It Should Be &lt;150 Ms. To Achieve This, Perform Static Test In Main Lobe And Keep Test Files Downloading In Background. Also, Ensure 4G Serving Cell Belongs To The Same Site. Exclude The Existing Logfile First
 5. Please update the AZQ app to version v3.2.822.apk specifically for the YouTube test.Kindly note that all other tests must continue to be performed using version v3.2.237.While performing the YouTube test, please ensure that the video is successfully playing in the script before saving the log file</t>
+  </si>
+  <si>
+    <t>15-Jan-2026 7:52 PM</t>
+  </si>
+  <si>
+    <t>15-Jan-2026 2:22 PM</t>
+  </si>
+  <si>
+    <t>15-Jan-2026 12:23 PM</t>
+  </si>
+  <si>
+    <t>CNTM32_BEN_P40</t>
+  </si>
+  <si>
+    <t>16-Jan-2026 11:08 PM</t>
+  </si>
+  <si>
+    <t>1. SCG addition after VoLTE call released
+2. Peak PDSCH DL Throughput
+3. UE Steering (Idle) : Non anchor/anchor to preferred anchor</t>
+  </si>
+  <si>
+    <t>1. Static VoLTE MO
+2. Static DL
+3. Static Idle</t>
+  </si>
+  <si>
+    <t>1. VoLTE Long Call MO – The SCG count after VoLTE call release should be equal to or greater than the total number of calls in the logfile. The KPI has failed because the SCG count is lower than the number of calls. Kindly exclude the existing logfile. While creating a new logfile, ensure the same site is serving in 4G and keep test files downloading in the background during static tests to support SCG addition.
+2. Peak PDSCH DL Throughput is not meeting the acceptance criteria, and if the value is 0, it indicates that it was not recorded in the logfile. Kindly exclude the logfile and create a new one, and verify the maximum value of PDSCH Throughput in the NR tab.
+3. For sites with NOKIA OEM, validate using Drive Idle, and for other OEMs, validate using Static Idle. In both Drive and Static Idle, the UE should latch from NR to LTE and from LTE to NR. In LTE, the UE should latch on the band that corresponds to the configured anchor layer.</t>
+  </si>
+  <si>
+    <t>BDAU57_BAD_P40</t>
+  </si>
+  <si>
+    <t>16-Jan-2026 7:34 PM</t>
+  </si>
+  <si>
+    <t>1. MT Call (pass/fail)
+2. SCG addition after VoLTE call released
+3. Peak Rank - 5G
+4. Video Streaming  (ms)</t>
+  </si>
+  <si>
+    <t>1. Static VoLTE MT
+2. Static VoLTE MO
+3. Static DL
+4. Static Yotube Streaming</t>
+  </si>
+  <si>
+    <t>1. VoLTE Long Call MT – As per Bharti acceptance criteria, a minimum of 3 successful call setups are required without any blocked call. Kindly perform at least 3 successful MT calls.
+2. VoLTE Long Call MO – The SCG count after VoLTE call release should be equal to or greater than the total number of calls in the logfile. The KPI has failed because the SCG count is lower than the number of calls. Kindly exclude the existing logfile. While creating a new logfile, ensure the same site is serving in 4G and keep test files downloading in the background during static tests to support SCG addition.
+3. Peak Rank is not meeting the acceptance criteria. Kindly redo the test and verify that the value meets the required threshold. To achieve the desired MCS, perform the test in the main lobe of the cell within a good coverage area.
+4. Please update the AZQ app to version v3.2.822.apk specifically for the YouTube test.Kindly note that all other tests must continue to be performed using version v3.2.237.While performing the YouTube test, please ensure that the video is successfully playing in the script before saving the log file</t>
+  </si>
+  <si>
+    <t>KO0796_KOL_P40</t>
+  </si>
+  <si>
+    <t>16-Jan-2026 7:12 PM</t>
+  </si>
+  <si>
+    <t>KTM113_KTM_P40</t>
+  </si>
+  <si>
+    <t>17-Jan-2026 10:56 AM</t>
+  </si>
+  <si>
+    <t>1. MT Call (pass/fail)
+2. SCG addition after VoLTE call released</t>
+  </si>
+  <si>
+    <t>1. Static VoLTE MT
+2. Static VoLTE MO</t>
+  </si>
+  <si>
+    <t>1. VoLTE Long Call MT – As per Bharti acceptance criteria, a minimum of 3 successful call setups are required without any blocked call. Kindly perform at least 3 successful MT calls.
+2. VoLTE Long Call MO – The SCG count after VoLTE call release should be equal to or greater than the total number of calls in the logfile. The KPI has failed because the SCG count is lower than the number of calls. Kindly exclude the existing logfile. While creating a new logfile, ensure the same site is serving in 4G and keep test files downloading in the background during static tests to support SCG addition.</t>
+  </si>
+  <si>
+    <t>BAE543_BAR_P40</t>
+  </si>
+  <si>
+    <t>16-Jan-2026 6:19 PM</t>
+  </si>
+  <si>
+    <t>19-Jan-2026 10:32 AM</t>
+  </si>
+  <si>
+    <t>HMIT12_KRN_P40</t>
+  </si>
+  <si>
+    <t>19-Jan-2026 12:31 AM</t>
+  </si>
+  <si>
+    <t>KCP174_KCP_P41</t>
+  </si>
+  <si>
+    <t>18-Jan-2026 4:36 PM</t>
+  </si>
+  <si>
+    <t>1. MO Call (pass/fail)
+2. MT Call (pass/fail)
+3. CSFB Call (pass/fail)
+4. SCG addition after VoLTE call released
+5. Ping/Round trip time(ms)
+6. Web Browsing - Top 10 Websites - Web page load time (ms)</t>
+  </si>
+  <si>
+    <t>1. Static VoLTE MO
+2. Static VoLTE MT
+3. Static CSFB MO
+4. Static VoLTE MO
+5. Static Ping
+6. Static Browsing (10 sites)</t>
+  </si>
+  <si>
+    <t>1. VoLTE Long Call MO – As per Bharti acceptance criteria, a minimum of 3 successful call setups are required without any blocked call. Kindly perform at least 3 successful MO calls.
+2. VoLTE Long Call MT – As per Bharti acceptance criteria, a minimum of 3 successful call setups are required without any blocked call. Kindly perform at least 3 successful MT calls.
+3. CSFB MO – As per Bharti acceptance criteria, a minimum of 3 successful call setups are required without any blocked call. Kindly perform at least 3 successful MO  calls.
+4. VoLTE Long Call MO – The SCG count after VoLTE call release should be equal to or greater than the total number of calls in the logfile. The KPI has failed because the SCG count is lower than the number of calls. Kindly exclude the existing logfile. While creating a new logfile, ensure the same site is serving in 4G and keep test files downloading in the background during static tests to support SCG addition.
+5. Ping is not meeting the acceptance criteria. The average ping value across all logfiles should be less than 50 ms. Kindly exclude the logfile where the average value exceeds 50 ms and redo the test.”
+6. While running the scripts, kindly verify in the Events tab that at least 10 websites are browsing. If not, exclude the logfile and create a new one.</t>
+  </si>
+  <si>
+    <t>GU3494_GJ_P40</t>
+  </si>
+  <si>
+    <t>18-Jan-2026 3:16 PM</t>
+  </si>
+  <si>
+    <t>AGR886_AGR_P40</t>
+  </si>
+  <si>
+    <t>18-Jan-2026 2:43 PM</t>
+  </si>
+  <si>
+    <t>1. CSFB Call (pass/fail)
+2. SCG addition after VoLTE call released
+3. Video Streaming  (ms)</t>
+  </si>
+  <si>
+    <t>1. CSFB MO – As per Bharti acceptance criteria, a minimum of 3 successful call setups are required without any blocked call. Kindly perform at least 3 successful MO  calls.
+2. VoLTE Long Call MO – The SCG count after VoLTE call release should be equal to or greater than the total number of calls in the logfile. The KPI has failed because the SCG count is lower than the number of calls. Kindly exclude the existing logfile. While creating a new logfile, ensure the same site is serving in 4G and keep test files downloading in the background during static tests to support SCG addition.
+3. Please update the AZQ app to version v3.2.822.apk specifically for the YouTube test.Kindly note that all other tests must continue to be performed using version v3.2.237.While performing the YouTube test, please ensure that the video is successfully playing in the script before saving the log file</t>
+  </si>
+  <si>
+    <t>BHGOP-60_PAT_P41</t>
+  </si>
+  <si>
+    <t>18-Jan-2026 2:18 PM</t>
+  </si>
+  <si>
+    <t>BHNGN-02_PAT_P40</t>
+  </si>
+  <si>
+    <t>17-Jan-2026 6:44 PM</t>
+  </si>
+  <si>
+    <t>1. eRAB setup success
+2. SCG addition after VoLTE call released
+3. Peak PUSCH UL Throughput
+4. Video Streaming  (ms)</t>
+  </si>
+  <si>
+    <t>1. Static ATDT
+2. Static VoLTE MO
+3. Static UL
+4. Static Yotube Streaming</t>
+  </si>
+  <si>
+    <t>1. Static ATDT – This is a 4G KPI. In ANTS, select the 4G filter and verify that the LTE Default EPS Bearer Request count matches the LTE Default EPS Bearer Activated count. If there is any mismatch, kindly exclude the logfile and create a new one.
+2. VoLTE Long Call MO – The SCG count after VoLTE call release should be equal to or greater than the total number of calls in the logfile. The KPI has failed because the SCG count is lower than the number of calls. Kindly exclude the existing logfile. While creating a new logfile, ensure the same site is serving in 4G and keep test files downloading in the background during static tests to support SCG addition.
+3. Peak PUSCH UL throughput is not meeting the acceptance criteria, and if the value is 0, it indicates that it was not recorded in the logfile. Kindly exclude the logfile and create a new one, and verify the maximum value of PUSCH Throughput in the NR tab.
+4. Please update the AZQ app to version v3.2.822.apk specifically for the YouTube test.Kindly note that all other tests must continue to be performed using version v3.2.237.While performing the YouTube test, please ensure that the video is successfully playing in the script before saving the log file</t>
+  </si>
+  <si>
+    <t>BHMOT-116_PAT_P40</t>
+  </si>
+  <si>
+    <t>17-Jan-2026 5:23 PM</t>
+  </si>
+  <si>
+    <t>1. RACH setup
+2. SCG addition after VoLTE call released
+3. Downlink Peak MCS - 5G
+4. Peak Rank - 5G
+5. SgNB Addition time (ms)
+6. Video Streaming  (ms)</t>
+  </si>
+  <si>
+    <t>1. Static All
+2. Static VoLTE MO
+3. Static DL
+4. Static DL
+5. Static ATDT
+6. Static Yotube Streaming</t>
+  </si>
+  <si>
+    <t>1. If DT Tool is  TEMS Pocket, verify the Static ATDT . The NR RACH Attempts should be equal to NR RACH Success; kindly exclude the logs where NR RACH has failed.
+If DT Tool is  AZQ, Validate Static All and ensure NR RACH Attempts match NR RACH Success. Please exclude the logs with NR RACH failures and redo the test accordingly.
+2. VoLTE Long Call MO – The SCG count after VoLTE call release should be equal to or greater than the total number of calls in the logfile. The KPI has failed because the SCG count is lower than the number of calls. Kindly exclude the existing logfile. While creating a new logfile, ensure the same site is serving in 4G and keep test files downloading in the background during static tests to support SCG addition.
+3. Peak MCS is not meeting the acceptance criteria. Kindly redo the test and verify that the value meets the required threshold. To achieve the desired MCS, perform the test in the main lobe of the cell within a good coverage area.
+4. Peak Rank is not meeting the acceptance criteria. Kindly redo the test and verify that the value meets the required threshold. To achieve the desired MCS, perform the test in the main lobe of the cell within a good coverage area.
+5. Exclue ATDT Logfile and Create New Sgnb Addition Time Is Very High. It Should Be &lt;150 Ms. To Achieve This, Perform Static Test In Main Lobe And Keep Test Files Downloading In Background. Also, Ensure 4G Serving Cell Belongs To The Same Site. Exclude The Existing Logfile First
+6. Please update the AZQ app to version v3.2.822.apk specifically for the YouTube test.Kindly note that all other tests must continue to be performed using version v3.2.237.While performing the YouTube test, please ensure that the video is successfully playing in the script before saving the log file</t>
+  </si>
+  <si>
+    <t>LABWL02_HP_P40</t>
+  </si>
+  <si>
+    <t>17-Jan-2026 4:49 PM</t>
+  </si>
+  <si>
+    <t>BHISS-02_PAT_P41</t>
+  </si>
+  <si>
+    <t>17-Jan-2026 4:14 PM</t>
+  </si>
+  <si>
+    <t>BHMOT-114_PAT_P40</t>
+  </si>
+  <si>
+    <t>17-Jan-2026 11:30 AM</t>
+  </si>
+  <si>
+    <t>1. SCG addition after VoLTE call released
+2. Downlink Peak MCS - 5G
+3. Peak Rank - 5G
+4. Peak PUSCH UL Throughput
+5. UE Steering (Idle) : Non anchor/anchor to preferred anchor
+6. Video Streaming  (ms)</t>
+  </si>
+  <si>
+    <t>1. Static VoLTE MO
+2. Static DL
+3. Static DL
+4. Static UL
+5. Static Idle
+6. Static Yotube Streaming</t>
+  </si>
+  <si>
+    <t>1. VoLTE Long Call MO – The SCG count after VoLTE call release should be equal to or greater than the total number of calls in the logfile. The KPI has failed because the SCG count is lower than the number of calls. Kindly exclude the existing logfile. While creating a new logfile, ensure the same site is serving in 4G and keep test files downloading in the background during static tests to support SCG addition.
+2. Peak MCS is not meeting the acceptance criteria. Kindly redo the test and verify that the value meets the required threshold. To achieve the desired MCS, perform the test in the main lobe of the cell within a good coverage area.
+3. Peak Rank is not meeting the acceptance criteria. Kindly redo the test and verify that the value meets the required threshold. To achieve the desired MCS, perform the test in the main lobe of the cell within a good coverage area.
+4. Peak PUSCH UL throughput is not meeting the acceptance criteria, and if the value is 0, it indicates that it was not recorded in the logfile. Kindly exclude the logfile and create a new one, and verify the maximum value of PUSCH Throughput in the NR tab.
+5. For sites with NOKIA OEM, validate using Drive Idle, and for other OEMs, validate using Static Idle. In both Drive and Static Idle, the UE should latch from NR to LTE and from LTE to NR. In LTE, the UE should latch on the band that corresponds to the configured anchor layer.
+6. Please update the AZQ app to version v3.2.822.apk specifically for the YouTube test.Kindly note that all other tests must continue to be performed using version v3.2.237.While performing the YouTube test, please ensure that the video is successfully playing in the script before saving the log file</t>
+  </si>
+  <si>
+    <t>CB1225_CBE_P40</t>
+  </si>
+  <si>
+    <t>19-Jan-2026 9:30 PM</t>
+  </si>
+  <si>
+    <t>MPID8975_Cluster Drive_IND_P40</t>
+  </si>
+  <si>
+    <t>19-Jan-2026 10:11 PM</t>
+  </si>
+  <si>
+    <t>1. Serving SSB beam steering
+2. eRAB setup success
+3. Downlink Peak MCS - 5G</t>
+  </si>
+  <si>
+    <t>1. Mobility DL
+2. Static ATDT
+3. Static DL</t>
+  </si>
+  <si>
+    <t>1. Kindly add drive coverage in the failed sector and verify that the Beam Index servings are meeting the acceptance criteria.
+2. Static ATDT – This is a 4G KPI. In ANTS, select the 4G filter and verify that the LTE Default EPS Bearer Request count matches the LTE Default EPS Bearer Activated count. If there is any mismatch, kindly exclude the logfile and create a new one.
+3. Peak MCS is not meeting the acceptance criteria. Kindly redo the test and verify that the value meets the required threshold. To achieve the desired MCS, perform the test in the main lobe of the cell within a good coverage area.</t>
+  </si>
+  <si>
+    <t>BHNEA-02_PAT_P40</t>
+  </si>
+  <si>
+    <t>19-Jan-2026 7:21 PM</t>
+  </si>
+  <si>
+    <t>BHCHA-94_PAT_P41</t>
+  </si>
+  <si>
+    <t>19-Jan-2026 2:21 PM</t>
+  </si>
+  <si>
+    <t>KAS78_RUD_P40</t>
+  </si>
+  <si>
+    <t>19-Jan-2026 2:19 PM</t>
+  </si>
+  <si>
+    <t>BHSAG-17_PAT_P40</t>
+  </si>
+  <si>
+    <t>19-Jan-2026 12:41 PM</t>
+  </si>
+  <si>
+    <t>1. Peak PUSCH UL Throughput
+2. UE Steering (Idle) : Non anchor/anchor to preferred anchor
+3. Video Streaming  (ms)</t>
+  </si>
+  <si>
+    <t>1. Static UL
+2. Static Idle
+3. Static Yotube Streaming</t>
+  </si>
+  <si>
+    <t>1. Peak PUSCH UL throughput is not meeting the acceptance criteria, and if the value is 0, it indicates that it was not recorded in the logfile. Kindly exclude the logfile and create a new one, and verify the maximum value of PUSCH Throughput in the NR tab.
+2. For sites with NOKIA OEM, validate using Drive Idle, and for other OEMs, validate using Static Idle. In both Drive and Static Idle, the UE should latch from NR to LTE and from LTE to NR. In LTE, the UE should latch on the band that corresponds to the configured anchor layer.
+3. Please update the AZQ app to version v3.2.822.apk specifically for the YouTube test.Kindly note that all other tests must continue to be performed using version v3.2.237.While performing the YouTube test, please ensure that the video is successfully playing in the script before saving the log file</t>
   </si>
 </sst>
 </file>
@@ -14973,7 +15287,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{450A2877-A455-427A-9170-EAD9C8461604}">
-  <dimension ref="A1:G1152"/>
+  <dimension ref="A1:G1178"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.6328125" bestFit="1" customWidth="1"/>
@@ -40009,6 +40323,604 @@
         <v>3356</v>
       </c>
     </row>
+    <row r="1153" spans="1:7" ht="57" x14ac:dyDescent="0.35">
+      <c r="A1153" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1153" s="8" t="s">
+        <v>3353</v>
+      </c>
+      <c r="C1153" s="7" t="s">
+        <v>3357</v>
+      </c>
+      <c r="D1153" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1153" s="10" t="s">
+        <v>2824</v>
+      </c>
+      <c r="F1153" s="11" t="s">
+        <v>2352</v>
+      </c>
+      <c r="G1153" s="12" t="s">
+        <v>2825</v>
+      </c>
+    </row>
+    <row r="1154" spans="1:7" ht="57" x14ac:dyDescent="0.35">
+      <c r="A1154" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1154" s="8" t="s">
+        <v>2586</v>
+      </c>
+      <c r="C1154" s="7" t="s">
+        <v>3358</v>
+      </c>
+      <c r="D1154" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1154" s="10" t="s">
+        <v>2588</v>
+      </c>
+      <c r="F1154" s="11" t="s">
+        <v>2589</v>
+      </c>
+      <c r="G1154" s="12" t="s">
+        <v>2590</v>
+      </c>
+    </row>
+    <row r="1155" spans="1:7" ht="38" x14ac:dyDescent="0.35">
+      <c r="A1155" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="B1155" s="8" t="s">
+        <v>3021</v>
+      </c>
+      <c r="C1155" s="7" t="s">
+        <v>3359</v>
+      </c>
+      <c r="D1155" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1155" s="10" t="s">
+        <v>2913</v>
+      </c>
+      <c r="F1155" s="11" t="s">
+        <v>2914</v>
+      </c>
+      <c r="G1155" s="12" t="s">
+        <v>2915</v>
+      </c>
+    </row>
+    <row r="1156" spans="1:7" ht="95" x14ac:dyDescent="0.35">
+      <c r="A1156" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1156" s="8" t="s">
+        <v>3360</v>
+      </c>
+      <c r="C1156" s="7" t="s">
+        <v>3361</v>
+      </c>
+      <c r="D1156" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1156" s="10" t="s">
+        <v>3362</v>
+      </c>
+      <c r="F1156" s="11" t="s">
+        <v>3363</v>
+      </c>
+      <c r="G1156" s="12" t="s">
+        <v>3364</v>
+      </c>
+    </row>
+    <row r="1157" spans="1:7" ht="104.5" x14ac:dyDescent="0.35">
+      <c r="A1157" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1157" s="8" t="s">
+        <v>3365</v>
+      </c>
+      <c r="C1157" s="7" t="s">
+        <v>3366</v>
+      </c>
+      <c r="D1157" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1157" s="10" t="s">
+        <v>3367</v>
+      </c>
+      <c r="F1157" s="11" t="s">
+        <v>3368</v>
+      </c>
+      <c r="G1157" s="12" t="s">
+        <v>3369</v>
+      </c>
+    </row>
+    <row r="1158" spans="1:7" ht="19" x14ac:dyDescent="0.35">
+      <c r="A1158" s="7" t="s">
+        <v>2201</v>
+      </c>
+      <c r="B1158" s="8" t="s">
+        <v>3370</v>
+      </c>
+      <c r="C1158" s="7" t="s">
+        <v>3371</v>
+      </c>
+      <c r="D1158" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1158" s="10" t="s">
+        <v>2705</v>
+      </c>
+      <c r="F1158" s="11" t="s">
+        <v>2706</v>
+      </c>
+      <c r="G1158" s="12" t="s">
+        <v>2707</v>
+      </c>
+    </row>
+    <row r="1159" spans="1:7" ht="57" x14ac:dyDescent="0.35">
+      <c r="A1159" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1159" s="8" t="s">
+        <v>3372</v>
+      </c>
+      <c r="C1159" s="7" t="s">
+        <v>3373</v>
+      </c>
+      <c r="D1159" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1159" s="10" t="s">
+        <v>3374</v>
+      </c>
+      <c r="F1159" s="11" t="s">
+        <v>3375</v>
+      </c>
+      <c r="G1159" s="12" t="s">
+        <v>3376</v>
+      </c>
+    </row>
+    <row r="1160" spans="1:7" ht="66.5" x14ac:dyDescent="0.35">
+      <c r="A1160" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1160" s="8" t="s">
+        <v>3377</v>
+      </c>
+      <c r="C1160" s="7" t="s">
+        <v>3378</v>
+      </c>
+      <c r="D1160" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1160" s="10" t="s">
+        <v>2425</v>
+      </c>
+      <c r="F1160" s="11" t="s">
+        <v>2426</v>
+      </c>
+      <c r="G1160" s="12" t="s">
+        <v>2427</v>
+      </c>
+    </row>
+    <row r="1161" spans="1:7" ht="57" x14ac:dyDescent="0.35">
+      <c r="A1161" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1161" s="8" t="s">
+        <v>3360</v>
+      </c>
+      <c r="C1161" s="7" t="s">
+        <v>3379</v>
+      </c>
+      <c r="D1161" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1161" s="10" t="s">
+        <v>2534</v>
+      </c>
+      <c r="F1161" s="11" t="s">
+        <v>2535</v>
+      </c>
+      <c r="G1161" s="12" t="s">
+        <v>2536</v>
+      </c>
+    </row>
+    <row r="1162" spans="1:7" ht="28.5" x14ac:dyDescent="0.35">
+      <c r="A1162" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="B1162" s="8" t="s">
+        <v>3380</v>
+      </c>
+      <c r="C1162" s="7" t="s">
+        <v>3381</v>
+      </c>
+      <c r="D1162" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1162" s="10" t="s">
+        <v>2356</v>
+      </c>
+      <c r="F1162" s="11" t="s">
+        <v>2357</v>
+      </c>
+      <c r="G1162" s="12" t="s">
+        <v>2358</v>
+      </c>
+    </row>
+    <row r="1163" spans="1:7" ht="133" x14ac:dyDescent="0.35">
+      <c r="A1163" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1163" s="8" t="s">
+        <v>3382</v>
+      </c>
+      <c r="C1163" s="7" t="s">
+        <v>3383</v>
+      </c>
+      <c r="D1163" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1163" s="10" t="s">
+        <v>3384</v>
+      </c>
+      <c r="F1163" s="11" t="s">
+        <v>3385</v>
+      </c>
+      <c r="G1163" s="12" t="s">
+        <v>3386</v>
+      </c>
+    </row>
+    <row r="1164" spans="1:7" ht="19" x14ac:dyDescent="0.35">
+      <c r="A1164" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1164" s="8" t="s">
+        <v>3387</v>
+      </c>
+      <c r="C1164" s="7" t="s">
+        <v>3388</v>
+      </c>
+      <c r="D1164" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1164" s="10" t="s">
+        <v>2505</v>
+      </c>
+      <c r="F1164" s="11" t="s">
+        <v>2506</v>
+      </c>
+      <c r="G1164" s="12" t="s">
+        <v>2507</v>
+      </c>
+    </row>
+    <row r="1165" spans="1:7" ht="85.5" x14ac:dyDescent="0.35">
+      <c r="A1165" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1165" s="8" t="s">
+        <v>3389</v>
+      </c>
+      <c r="C1165" s="7" t="s">
+        <v>3390</v>
+      </c>
+      <c r="D1165" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1165" s="10" t="s">
+        <v>3391</v>
+      </c>
+      <c r="F1165" s="11" t="s">
+        <v>3084</v>
+      </c>
+      <c r="G1165" s="12" t="s">
+        <v>3392</v>
+      </c>
+    </row>
+    <row r="1166" spans="1:7" ht="38" x14ac:dyDescent="0.35">
+      <c r="A1166" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1166" s="8" t="s">
+        <v>3393</v>
+      </c>
+      <c r="C1166" s="7" t="s">
+        <v>3394</v>
+      </c>
+      <c r="D1166" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1166" s="10" t="s">
+        <v>2529</v>
+      </c>
+      <c r="F1166" s="11" t="s">
+        <v>2530</v>
+      </c>
+      <c r="G1166" s="12" t="s">
+        <v>2531</v>
+      </c>
+    </row>
+    <row r="1167" spans="1:7" ht="123.5" x14ac:dyDescent="0.35">
+      <c r="A1167" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1167" s="8" t="s">
+        <v>3395</v>
+      </c>
+      <c r="C1167" s="7" t="s">
+        <v>3396</v>
+      </c>
+      <c r="D1167" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1167" s="10" t="s">
+        <v>3397</v>
+      </c>
+      <c r="F1167" s="11" t="s">
+        <v>3398</v>
+      </c>
+      <c r="G1167" s="12" t="s">
+        <v>3399</v>
+      </c>
+    </row>
+    <row r="1168" spans="1:7" ht="171" x14ac:dyDescent="0.35">
+      <c r="A1168" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1168" s="8" t="s">
+        <v>3400</v>
+      </c>
+      <c r="C1168" s="7" t="s">
+        <v>3401</v>
+      </c>
+      <c r="D1168" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1168" s="10" t="s">
+        <v>3402</v>
+      </c>
+      <c r="F1168" s="11" t="s">
+        <v>3403</v>
+      </c>
+      <c r="G1168" s="12" t="s">
+        <v>3404</v>
+      </c>
+    </row>
+    <row r="1169" spans="1:7" ht="38" x14ac:dyDescent="0.35">
+      <c r="A1169" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="B1169" s="8" t="s">
+        <v>3405</v>
+      </c>
+      <c r="C1169" s="7" t="s">
+        <v>3406</v>
+      </c>
+      <c r="D1169" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1169" s="10" t="s">
+        <v>2913</v>
+      </c>
+      <c r="F1169" s="11" t="s">
+        <v>2914</v>
+      </c>
+      <c r="G1169" s="12" t="s">
+        <v>2915</v>
+      </c>
+    </row>
+    <row r="1170" spans="1:7" ht="19" x14ac:dyDescent="0.35">
+      <c r="A1170" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1170" s="8" t="s">
+        <v>3407</v>
+      </c>
+      <c r="C1170" s="7" t="s">
+        <v>3408</v>
+      </c>
+      <c r="D1170" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1170" s="10" t="s">
+        <v>2402</v>
+      </c>
+      <c r="F1170" s="11" t="s">
+        <v>2357</v>
+      </c>
+      <c r="G1170" s="12" t="s">
+        <v>2430</v>
+      </c>
+    </row>
+    <row r="1171" spans="1:7" ht="161.5" x14ac:dyDescent="0.35">
+      <c r="A1171" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1171" s="8" t="s">
+        <v>3409</v>
+      </c>
+      <c r="C1171" s="7" t="s">
+        <v>3410</v>
+      </c>
+      <c r="D1171" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1171" s="10" t="s">
+        <v>3411</v>
+      </c>
+      <c r="F1171" s="11" t="s">
+        <v>3412</v>
+      </c>
+      <c r="G1171" s="12" t="s">
+        <v>3413</v>
+      </c>
+    </row>
+    <row r="1172" spans="1:7" ht="28.5" x14ac:dyDescent="0.35">
+      <c r="A1172" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1172" s="8" t="s">
+        <v>3414</v>
+      </c>
+      <c r="C1172" s="7" t="s">
+        <v>3415</v>
+      </c>
+      <c r="D1172" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1172" s="10" t="s">
+        <v>2356</v>
+      </c>
+      <c r="F1172" s="11" t="s">
+        <v>2357</v>
+      </c>
+      <c r="G1172" s="12" t="s">
+        <v>2358</v>
+      </c>
+    </row>
+    <row r="1173" spans="1:7" ht="66.5" x14ac:dyDescent="0.35">
+      <c r="A1173" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1173" s="8" t="s">
+        <v>3416</v>
+      </c>
+      <c r="C1173" s="7" t="s">
+        <v>3417</v>
+      </c>
+      <c r="D1173" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1173" s="10" t="s">
+        <v>3418</v>
+      </c>
+      <c r="F1173" s="11" t="s">
+        <v>3419</v>
+      </c>
+      <c r="G1173" s="12" t="s">
+        <v>3420</v>
+      </c>
+    </row>
+    <row r="1174" spans="1:7" ht="161.5" x14ac:dyDescent="0.35">
+      <c r="A1174" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1174" s="8" t="s">
+        <v>3421</v>
+      </c>
+      <c r="C1174" s="7" t="s">
+        <v>3422</v>
+      </c>
+      <c r="D1174" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1174" s="10" t="s">
+        <v>3411</v>
+      </c>
+      <c r="F1174" s="11" t="s">
+        <v>3412</v>
+      </c>
+      <c r="G1174" s="12" t="s">
+        <v>3413</v>
+      </c>
+    </row>
+    <row r="1175" spans="1:7" ht="57" x14ac:dyDescent="0.35">
+      <c r="A1175" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1175" s="8" t="s">
+        <v>3423</v>
+      </c>
+      <c r="C1175" s="7" t="s">
+        <v>3424</v>
+      </c>
+      <c r="D1175" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1175" s="10" t="s">
+        <v>2746</v>
+      </c>
+      <c r="F1175" s="11" t="s">
+        <v>2583</v>
+      </c>
+      <c r="G1175" s="12" t="s">
+        <v>2747</v>
+      </c>
+    </row>
+    <row r="1176" spans="1:7" ht="47.5" x14ac:dyDescent="0.35">
+      <c r="A1176" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1176" s="8" t="s">
+        <v>3425</v>
+      </c>
+      <c r="C1176" s="7" t="s">
+        <v>3426</v>
+      </c>
+      <c r="D1176" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1176" s="10" t="s">
+        <v>2332</v>
+      </c>
+      <c r="F1176" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="G1176" s="12" t="s">
+        <v>2334</v>
+      </c>
+    </row>
+    <row r="1177" spans="1:7" ht="133" x14ac:dyDescent="0.35">
+      <c r="A1177" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1177" s="8" t="s">
+        <v>3382</v>
+      </c>
+      <c r="C1177" s="7" t="s">
+        <v>3383</v>
+      </c>
+      <c r="D1177" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1177" s="10" t="s">
+        <v>3384</v>
+      </c>
+      <c r="F1177" s="11" t="s">
+        <v>3385</v>
+      </c>
+      <c r="G1177" s="12" t="s">
+        <v>3386</v>
+      </c>
+    </row>
+    <row r="1178" spans="1:7" ht="85.5" x14ac:dyDescent="0.35">
+      <c r="A1178" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1178" s="8" t="s">
+        <v>3427</v>
+      </c>
+      <c r="C1178" s="7" t="s">
+        <v>3428</v>
+      </c>
+      <c r="D1178" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1178" s="10" t="s">
+        <v>3429</v>
+      </c>
+      <c r="F1178" s="11" t="s">
+        <v>3430</v>
+      </c>
+      <c r="G1178" s="12" t="s">
+        <v>3431</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
